--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487769_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487769_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2461</v>
+        <v>4.9451</v>
       </c>
       <c r="E2" t="n">
-        <v>3.774</v>
+        <v>6.1202</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4721</v>
+        <v>-1.1751</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1704</v>
+        <v>1.5212</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1916</v>
+        <v>2.8422</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0212</v>
+        <v>-1.321</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5626</v>
+        <v>3.5136</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4451</v>
+        <v>4.1978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1176</v>
+        <v>-0.6842</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3922</v>
+        <v>-1.9924</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2535</v>
+        <v>-1.3556</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1388</v>
+        <v>-0.6368</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2589</v>
+        <v>0.6539</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9971</v>
+        <v>0.2715</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2618</v>
+        <v>0.3824</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1061</v>
+        <v>1.5213</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3361</v>
+        <v>2.3351</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>I. ROYO ARGOTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1504</v>
+        <v>1.754</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0905</v>
+        <v>1.3569</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9402</v>
+        <v>0.397</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5212</v>
+        <v>0.3594</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8422</v>
+        <v>2.0233</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.321</v>
+        <v>-1.6639</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5136</v>
+        <v>0.7923</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1978</v>
+        <v>2.3174</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6842</v>
+        <v>-1.5251</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9924</v>
+        <v>-0.4328</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3556</v>
+        <v>-0.294</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6368</v>
+        <v>-0.1388</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1409</v>
+        <v>1.0001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7581</v>
+        <v>0.4377</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6172</v>
+        <v>0.5624</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5213</v>
+        <v>-0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3351</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8137</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ROYO ARGOTE</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0651</v>
+        <v>1.7492</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7855</v>
+        <v>1.9524</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2796</v>
+        <v>-0.2032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3594</v>
+        <v>2.1704</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0233</v>
+        <v>2.1916</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6639</v>
+        <v>-0.0212</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7923</v>
+        <v>3.5626</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3174</v>
+        <v>3.4451</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5251</v>
+        <v>0.1176</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4328</v>
+        <v>-1.3922</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.294</v>
+        <v>-1.2535</v>
       </c>
       <c r="O4" t="n">
         <v>-0.1388</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6244</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3113</v>
+        <v>1.762</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8663</v>
+        <v>1.1754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.445</v>
+        <v>0.5866</v>
       </c>
       <c r="V4" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="X4" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1675</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.3975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1606</v>
+        <v>-1.0883</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4561</v>
+        <v>0.0974</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7045</v>
+        <v>-1.1857</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6004</v>
+        <v>-1.7841</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4416</v>
+        <v>-3.4692</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.042</v>
+        <v>1.6851</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1919</v>
+        <v>-0.4735</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4989</v>
+        <v>-2.6892</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.6908</v>
+        <v>2.2158</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4085</v>
+        <v>-1.3106</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0573</v>
+        <v>-0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3512</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,28 +844,28 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4398</v>
+        <v>0.6958</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7764</v>
+        <v>0.4439</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3366</v>
+        <v>0.2519</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1077</v>
+        <v>-1.386</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0394</v>
+        <v>-1.0338</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0682</v>
+        <v>-0.3522</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7841</v>
+        <v>-2.6004</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.4692</v>
+        <v>0.4416</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6851</v>
+        <v>-3.042</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4735</v>
+        <v>-1.1919</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6892</v>
+        <v>0.4989</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2158</v>
+        <v>-1.6908</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3106</v>
+        <v>-1.4085</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.78</v>
+        <v>-0.0573</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-1.3512</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,22 +922,22 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3236</v>
+        <v>1.2144</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6929</v>
+        <v>1.1987</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3693</v>
+        <v>0.0157</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7257</v>
+        <v>-2.1834</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6522</v>
+        <v>-2.0512</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0735</v>
+        <v>-0.1323</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2022</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2112</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8358</v>
+        <v>-0.2347</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0823</v>
+        <v>0.0235</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9376</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0934</v>
+        <v>-3.3409</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9696</v>
+        <v>-5.0115</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8761</v>
+        <v>1.6706</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9309</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6054</v>
+        <v>0.358</v>
       </c>
       <c r="T8" t="n">
-        <v>0.152</v>
+        <v>0.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4535</v>
+        <v>0.248</v>
       </c>
       <c r="V8" t="n">
         <v>0.9376</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.875</v>
+        <v>-3.7076</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9164</v>
+        <v>-4.1307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0414</v>
+        <v>0.4231</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3995</v>
@@ -1156,13 +1156,13 @@
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.308</v>
+        <v>-0.1406</v>
       </c>
       <c r="T9" t="n">
-        <v>0.152</v>
+        <v>-0.0624</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4599</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7513</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.5611</v>
+        <v>-7.4777</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1923</v>
+        <v>-5.5494</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3688</v>
+        <v>-1.9284</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4815</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4771</v>
+        <v>-0.3937</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7705</v>
+        <v>-0.1276</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7065</v>
+        <v>-0.2661</v>
       </c>
       <c r="V10" t="n">
         <v>-2.6889</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.0619</v>
+        <v>-10.7356</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.576000000000001</v>
+        <v>-8.249700000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.486</v>
+        <v>-2.4862</v>
       </c>
       <c r="G11" t="n">
         <v>-5.3476</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7144000000000008</v>
+        <v>0.7143999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-6.061999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6346000000000005</v>
+        <v>0.6345999999999996</v>
       </c>
       <c r="K11" t="n">
-        <v>5.839499999999999</v>
+        <v>5.839500000000001</v>
       </c>
       <c r="L11" t="n">
         <v>-5.2047</v>
@@ -1312,10 +1312,10 @@
         <v>11.4464</v>
       </c>
       <c r="S11" t="n">
-        <v>4.612299999999999</v>
+        <v>4.9387</v>
       </c>
       <c r="T11" t="n">
-        <v>2.886500000000001</v>
+        <v>3.2125</v>
       </c>
       <c r="U11" t="n">
         <v>1.7261</v>
@@ -1324,7 +1324,7 @@
         <v>-3.0428</v>
       </c>
       <c r="W11" t="n">
-        <v>6.633700000000001</v>
+        <v>6.6337</v>
       </c>
       <c r="X11" t="n">
         <v>-9.676300000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.1909</v>
+        <v>6.4131</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5937</v>
+        <v>4.2366</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5972</v>
+        <v>2.1765</v>
       </c>
       <c r="G12" t="n">
         <v>3.1944</v>
@@ -1390,13 +1390,13 @@
         <v>2.4974</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7954</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2396</v>
+        <v>-0.5967</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5558</v>
+        <v>0.0235</v>
       </c>
       <c r="V12" t="n">
         <v>2.3351</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7967</v>
+        <v>4.3809</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2479</v>
+        <v>2.4622</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5488</v>
+        <v>1.9187</v>
       </c>
       <c r="G13" t="n">
         <v>2.8542</v>
@@ -1468,13 +1468,13 @@
         <v>2.7055</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5331</v>
+        <v>-0.9489</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.721</v>
+        <v>-0.5067</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8122</v>
+        <v>-0.4423</v>
       </c>
       <c r="V13" t="n">
         <v>-0.23</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2384</v>
+        <v>2.434</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3115</v>
+        <v>2.0239</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5499</v>
+        <v>0.4101</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4735</v>
+        <v>1.4979</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6418</v>
+        <v>0.9656</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1152</v>
+        <v>0.5323</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.2736</v>
+        <v>2.2044</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.352</v>
+        <v>2.1742</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0784</v>
+        <v>0.0302</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7471</v>
+        <v>-0.7065</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7102000000000001</v>
+        <v>-1.2086</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0369</v>
+        <v>0.5021</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8731</v>
+        <v>2.4974</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5756</v>
+        <v>0.063</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6458</v>
+        <v>0.2763</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9298</v>
+        <v>-0.2133</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3975</v>
+        <v>-0.5838</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>0.5838</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2446</v>
+        <v>2.3953</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9355</v>
+        <v>1.6149</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3091</v>
+        <v>0.7804</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2938</v>
+        <v>2.7438</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6097</v>
+        <v>-1.6567</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.316</v>
+        <v>4.4005</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9388</v>
+        <v>2.4012</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8996</v>
+        <v>-1.0686</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0392</v>
+        <v>3.4698</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.645</v>
+        <v>0.3426</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2899</v>
+        <v>-0.5881</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3551</v>
+        <v>0.9307</v>
       </c>
       <c r="P15" t="n">
         <v>0.8325</v>
@@ -1624,28 +1624,28 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2859</v>
+        <v>-0.3673</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0373</v>
+        <v>-0.3295</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2486</v>
+        <v>-0.0378</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1981</v>
+        <v>2.1615</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8095</v>
+        <v>-2.0616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3886</v>
+        <v>4.223</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4979</v>
+        <v>0.4735</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9656</v>
+        <v>-0.6418</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5323</v>
+        <v>1.1152</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2044</v>
+        <v>-1.2736</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1742</v>
+        <v>-1.352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0302</v>
+        <v>0.0784</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7065</v>
+        <v>1.7471</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2086</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5021</v>
+        <v>1.0369</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4568</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4974</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1729</v>
+        <v>0.4986</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0619</v>
+        <v>-0.1043</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2348</v>
+        <v>0.6029</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8707</v>
+        <v>1.8309</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6149</v>
+        <v>-0.8368</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2559</v>
+        <v>2.6677</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7438</v>
+        <v>1.4145</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6567</v>
+        <v>1.1173</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4005</v>
+        <v>0.2972</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4012</v>
+        <v>-0.4713</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0686</v>
+        <v>0.8399</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4698</v>
+        <v>-1.3112</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3426</v>
+        <v>1.8858</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5881</v>
+        <v>0.2775</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9307</v>
+        <v>1.6084</v>
       </c>
       <c r="P17" t="n">
         <v>0.8325</v>
@@ -1780,28 +1780,28 @@
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8919</v>
+        <v>-0.646</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3295</v>
+        <v>-0.7224</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5623</v>
+        <v>0.0764</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8137</v>
+        <v>0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5427</v>
+        <v>1.7088</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1583</v>
+        <v>1.3997</v>
       </c>
       <c r="F18" t="n">
-        <v>2.701</v>
+        <v>0.3091</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4145</v>
+        <v>1.2938</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1173</v>
+        <v>1.6097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2972</v>
+        <v>-0.316</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4713</v>
+        <v>1.9388</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8399</v>
+        <v>1.8996</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3112</v>
+        <v>0.0392</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8858</v>
+        <v>-0.645</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2775</v>
+        <v>-0.2899</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6084</v>
+        <v>-0.3551</v>
       </c>
       <c r="P18" t="n">
         <v>0.8325</v>
@@ -1858,19 +1858,19 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9342</v>
+        <v>0.7501</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0439</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1097</v>
+        <v>0.2486</v>
       </c>
       <c r="V18" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6109</v>
+        <v>-0.5855</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0261</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5848</v>
+        <v>-0.5594</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5078</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1031</v>
+        <v>-0.0776</v>
       </c>
       <c r="T19" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0378</v>
+        <v>-0.0124</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3592</v>
+        <v>-1.5109</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2435</v>
+        <v>-0.3994</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6028</v>
+        <v>-1.1115</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6735</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3725</v>
+        <v>-0.5242</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7763</v>
+        <v>0.1334</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1489</v>
+        <v>-0.6576</v>
       </c>
       <c r="V20" t="n">
         <v>0.23</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9246</v>
+        <v>-2.2841</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6888</v>
+        <v>-0.3673</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2358</v>
+        <v>-1.9168</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2247</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4699</v>
+        <v>-0.8294</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.2657</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8827</v>
+        <v>-0.5637</v>
       </c>
       <c r="V21" t="n">
         <v>0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1256</v>
+        <v>-3.739</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7745</v>
+        <v>-5.5602</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6489</v>
+        <v>1.8212</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7186</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2009</v>
+        <v>0.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.261</v>
+        <v>-0.0467</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06</v>
+        <v>0.2323</v>
       </c>
       <c r="V22" t="n">
         <v>0.7076</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>11.0618</v>
+        <v>13.205</v>
       </c>
       <c r="E23" t="n">
-        <v>2.485799999999999</v>
+        <v>2.485900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>8.575999999999999</v>
+        <v>10.719</v>
       </c>
       <c r="G23" t="n">
         <v>5.3475</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7146000000000005</v>
+        <v>-0.7146</v>
       </c>
       <c r="I23" t="n">
         <v>6.0619</v>
@@ -2224,7 +2224,7 @@
         <v>5.982200000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>5.125</v>
+        <v>5.124999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>0.8571999999999995</v>
@@ -2248,13 +2248,13 @@
         <v>18.7307</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.6124</v>
+        <v>-2.4692</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7261</v>
+        <v>-1.726</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.8864</v>
+        <v>-0.7433999999999998</v>
       </c>
       <c r="V23" t="n">
         <v>3.042800000000001</v>
